--- a/resources/templates/SOA_Template_Final.xlsx
+++ b/resources/templates/SOA_Template_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpatsz/Desktop/Capstone - Lantaka/Capstone_Lantaka_Reservation_System/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6FDCDF-6772-3640-BFE9-6019D83C79B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6312FC-DC7A-0349-B034-0C1BAFA51D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="780" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOA FOR ACCOMODATION" sheetId="3" r:id="rId1"/>
@@ -469,15 +469,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="39" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,25 +508,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="39" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -564,6 +546,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="39" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2117,9 +2117,9 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2127,9 +2127,9 @@
       <c r="B12" s="3"/>
       <c r="E12" s="7"/>
       <c r="G12" s="19"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2141,9 +2141,9 @@
       <c r="D13" s="4"/>
       <c r="E13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -2177,8 +2177,8 @@
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="36"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="32"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="2"/>
@@ -2190,8 +2190,8 @@
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="36"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="32"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="2"/>
@@ -2203,53 +2203,53 @@
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="37"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="33"/>
       <c r="E18" s="12"/>
       <c r="K18" s="18"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="39"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
       <c r="K19" s="18"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="52"/>
+      <c r="D20" s="43"/>
       <c r="K20" s="18"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="C21" s="65"/>
+      <c r="C21" s="55"/>
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40" t="s">
+      <c r="I22" s="36"/>
+      <c r="J22" s="36" t="s">
         <v>6</v>
       </c>
       <c r="K22" s="1"/>
@@ -2257,16 +2257,16 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="44">
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="40">
         <v>3600</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="45">
+      <c r="I23" s="40"/>
+      <c r="J23" s="41">
         <f>G23*E23</f>
         <v>0</v>
       </c>
@@ -2275,27 +2275,27 @@
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="57"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="47"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="57">
+      <c r="C25" s="37"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="47">
         <f>G25*E25</f>
         <v>0</v>
       </c>
@@ -2304,14 +2304,14 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="57">
+      <c r="C26" s="37"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="47">
         <f>G26*E26</f>
         <v>0</v>
       </c>
@@ -2320,72 +2320,88 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="63"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="63"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="D29" s="46"/>
-      <c r="G29" s="48" t="s">
+      <c r="C29" s="24"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="49">
+      <c r="H29" s="62">
         <v>42895.68</v>
       </c>
-      <c r="I29" s="50"/>
-      <c r="J29" s="51">
+      <c r="I29" s="63"/>
+      <c r="J29" s="64">
         <f>SUM(J23:J24)</f>
         <v>0</v>
       </c>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="21"/>
       <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="26"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="65"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="27"/>
-      <c r="G32" s="54" t="s">
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="28">
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="67">
         <f>SUM(J29)</f>
         <v>0</v>
       </c>
@@ -2394,21 +2410,27 @@
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="27"/>
-      <c r="J33" s="21"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="31"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="1"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2419,7 +2441,7 @@
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="53"/>
+      <c r="C36" s="44"/>
       <c r="K36" s="1"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2483,7 +2505,7 @@
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
-      <c r="G43" s="33"/>
+      <c r="G43" s="29"/>
       <c r="H43" s="2"/>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
@@ -2596,22 +2618,22 @@
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="P65" s="35"/>
+      <c r="P65" s="31"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="P66" s="35"/>
+      <c r="P66" s="31"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="P67" s="35"/>
+      <c r="P67" s="31"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="P68" s="35"/>
+      <c r="P68" s="31"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
@@ -2668,8 +2690,8 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
-      <c r="S84" s="32"/>
-      <c r="T84" s="34"/>
+      <c r="S84" s="28"/>
+      <c r="T84" s="30"/>
       <c r="U84" s="15"/>
       <c r="V84" s="15"/>
     </row>
